--- a/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/ExcelFiles/Monster.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\2D_Evaulation\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22580" windowHeight="11270"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="18852" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,33 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
+    <x:t>Prefabs/2D/Enemy</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
   </x:si>
   <x:si>
     <x:t>도그</x:t>
@@ -54,10 +36,19 @@
     <x:t>피그미</x:t>
   </x:si>
   <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
@@ -66,16 +57,28 @@
     <x:t>mob_slim_1</x:t>
   </x:si>
   <x:si>
-    <x:t>mob_dog_1</x:t>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>mob_pigme_1</x:t>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
   <x:si>
     <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
@@ -179,16 +182,16 @@
   <x:borders count="3">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -226,8 +229,8 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="17">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
@@ -880,16 +883,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="63.22265625" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="23.22265625" style="3" customWidth="1"/>
     <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
     <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
     <x:col min="7" max="16384" width="12.54296875" style="3"/>
@@ -897,64 +898,64 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.19999999999999928946">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="15"/>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="5"/>
       <x:c r="E4" s="5"/>
@@ -971,13 +972,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
         <x:v>15</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="5"/>
       <x:c r="E5" s="5"/>
@@ -994,16 +995,18 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
+      <x:c r="E6" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
@@ -2240,7 +2243,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>